--- a/importaciones_productos/FV21553 registro productos.xlsx
+++ b/importaciones_productos/FV21553 registro productos.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FRASANGALUn</t>
+          <t>FRASANmL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -518,11 +518,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>303700</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +536,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>FRAOCE500Un</t>
+          <t>FRAOCEmL</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -551,11 +551,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>34300</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FRALIM500Un</t>
+          <t>FRALIMmL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -584,11 +584,11 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>29800</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="5">
@@ -602,7 +602,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FRAKIW500Un</t>
+          <t>FRAKIWmL</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -617,11 +617,11 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>36300</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -635,7 +635,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>FRAPIN500Un</t>
+          <t>FRAPINmL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>33000</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -668,7 +668,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>FRACOC500Un</t>
+          <t>FRACOCmL</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -683,11 +683,11 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>29800</v>
+        <v>59.6</v>
       </c>
     </row>
   </sheetData>
